--- a/eduservices/DRILL_SIMULATION.xlsx
+++ b/eduservices/DRILL_SIMULATION.xlsx
@@ -748,7 +748,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Pourquoi l'EBITDA de TUNON_PAR recule de 10 500 € : la croissance existe, les coûts fixes la mangent</a:t>
+              <a:t>EBITDA TUNON_PAR  ·  2025 → 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -899,8 +899,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="150000"/>
-          <min val="80000"/>
+          <max val="145000"/>
+          <min val="90000"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -912,7 +912,7 @@
         <majorUnit val="10000"/>
       </valAx>
     </plotArea>
-    <plotVisOnly val="1"/>
+    <plotVisOnly val="0"/>
     <dispBlanksAs val="gap"/>
   </chart>
 </chartSpace>
